--- a/sample/受注台帳.xlsx
+++ b/sample/受注台帳.xlsx
@@ -8,46 +8,6 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'受注台帳'!$1:$1</definedName>
   </definedNames>
 </workbook>
-</file>
-
-<file path=xl/joPython.xml><?xml version="1.0" encoding="utf-8"?>
-<joPython>
-  <script name="取り込み"># 店(catalog_server)に溜まった注文を台帳へ追記する。
-# 実行は「@取り込み net」(網あり檻 — 許可はその場の操作だけ)。
-# 取込済の件数(K2)を控えているので、新しい注文だけが入る。
-URL = "http://127.0.0.1:8765"
-import urllib.request, json, csv, io
-orders = json.loads(urllib.request.urlopen(URL + "/orders", timeout=5).read().decode("utf-8"))
-raw = urllib.request.urlopen(URL + "/catalog.csv", timeout=5).read().decode("utf-8")
-master = {r[0]: (r[2], int(r[4])) for r in list(csv.reader(io.StringIO(raw)))[1:]}
-done = int(float(s["K2"] or 0))
-new = orders[done:]
-if not new:
-    print(f"新しい注文はありません(累計 {len(orders)} 件)")
-else:
-    n = 2
-    while s[f"A{n}"] not in (None, ""):
-        n += 1
-    lines = 0
-    for i, o in enumerate(new, start=done + 1):
-        for line in o.get("明細", []):
-            code = str(line.get("品番", ""))
-            name, price = master.get(code, ("(不明な品番)", 0))
-            s[f"A{n}"] = i
-            s[f"B{n}"] = o.get("社名", "")
-            s[f"C{n}"] = code
-            s[f"D{n}"] = name
-            s[f"E{n}"] = int(line.get("数量", 0))
-            s[f"F{n}"] = price
-            s[f"G{n}"] = f"=E{n}*F{n}"
-            s[f"H{n}"] = "FALSE"
-            n += 1
-            lines += 1
-    s["K2"] = len(orders)
-    b.recalc()
-    print(f"{len(new)} 件({lines} 行)を取り込みました(累計 {len(orders)} 件)")
-</script>
-</joPython>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
